--- a/dev/StructureDefinition-bc-address.xlsx
+++ b/dev/StructureDefinition-bc-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1505,7 +1505,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>105</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>111</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -3099,12 +3099,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN18">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
